--- a/Tutorials/tutorial_10_input.xlsx
+++ b/Tutorials/tutorial_10_input.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericmasson/Dropbox/VPIPV python/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ericmasson/Dropbox/VPIPV python/Equilibrist_032826_PAPER/TUTORIALS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{057B78EB-7B26-A049-9965-178A8BC25ADE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A24664-C52D-D344-8D9C-0A09B2C9407B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="6840" yWindow="7840" windowWidth="22140" windowHeight="10400" xr2:uid="{91C0E864-DD14-2549-A639-D173B2832451}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="780" yWindow="1560" windowWidth="28660" windowHeight="15560" activeTab="1" xr2:uid="{91C0E864-DD14-2549-A639-D173B2832451}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,16 +38,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>V</t>
+  </si>
+  <si>
+    <t>cage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -60,6 +63,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -69,7 +78,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -77,13 +86,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10360,14 +10387,752 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB6E04DE-6D58-D14E-A7D3-4FC117471F84}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:DR2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="122" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:122" x14ac:dyDescent="0.2">
+      <c r="B1" s="1">
+        <v>210</v>
+      </c>
+      <c r="C1" s="1">
+        <v>211</v>
+      </c>
+      <c r="D1" s="1">
+        <v>212</v>
+      </c>
+      <c r="E1" s="1">
+        <v>213</v>
+      </c>
+      <c r="F1" s="1">
+        <v>214</v>
+      </c>
+      <c r="G1" s="1">
+        <v>215</v>
+      </c>
+      <c r="H1" s="1">
+        <v>216</v>
+      </c>
+      <c r="I1" s="1">
+        <v>217</v>
+      </c>
+      <c r="J1" s="1">
+        <v>218</v>
+      </c>
+      <c r="K1" s="1">
+        <v>219</v>
+      </c>
+      <c r="L1" s="1">
+        <v>220</v>
+      </c>
+      <c r="M1" s="1">
+        <v>221</v>
+      </c>
+      <c r="N1" s="1">
+        <v>222</v>
+      </c>
+      <c r="O1" s="1">
+        <v>223</v>
+      </c>
+      <c r="P1" s="1">
+        <v>224</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>225</v>
+      </c>
+      <c r="R1" s="1">
+        <v>226</v>
+      </c>
+      <c r="S1" s="1">
+        <v>227</v>
+      </c>
+      <c r="T1" s="1">
+        <v>228</v>
+      </c>
+      <c r="U1" s="1">
+        <v>229</v>
+      </c>
+      <c r="V1" s="1">
+        <v>230</v>
+      </c>
+      <c r="W1" s="1">
+        <v>231</v>
+      </c>
+      <c r="X1" s="1">
+        <v>232</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>233</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>234</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>235</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>236</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>237</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>238</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>239</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>240</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>241</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>242</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>243</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>244</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>245</v>
+      </c>
+      <c r="AL1" s="1">
+        <v>246</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>247</v>
+      </c>
+      <c r="AN1" s="1">
+        <v>248</v>
+      </c>
+      <c r="AO1" s="1">
+        <v>249</v>
+      </c>
+      <c r="AP1" s="1">
+        <v>250</v>
+      </c>
+      <c r="AQ1" s="1">
+        <v>251</v>
+      </c>
+      <c r="AR1" s="1">
+        <v>252</v>
+      </c>
+      <c r="AS1" s="1">
+        <v>253</v>
+      </c>
+      <c r="AT1" s="1">
+        <v>254</v>
+      </c>
+      <c r="AU1" s="1">
+        <v>255</v>
+      </c>
+      <c r="AV1" s="1">
+        <v>256</v>
+      </c>
+      <c r="AW1" s="1">
+        <v>257</v>
+      </c>
+      <c r="AX1" s="1">
+        <v>258</v>
+      </c>
+      <c r="AY1" s="1">
+        <v>259</v>
+      </c>
+      <c r="AZ1" s="1">
+        <v>260</v>
+      </c>
+      <c r="BA1" s="1">
+        <v>261</v>
+      </c>
+      <c r="BB1" s="1">
+        <v>262</v>
+      </c>
+      <c r="BC1" s="1">
+        <v>263</v>
+      </c>
+      <c r="BD1" s="1">
+        <v>264</v>
+      </c>
+      <c r="BE1" s="1">
+        <v>265</v>
+      </c>
+      <c r="BF1" s="1">
+        <v>266</v>
+      </c>
+      <c r="BG1" s="1">
+        <v>267</v>
+      </c>
+      <c r="BH1" s="1">
+        <v>268</v>
+      </c>
+      <c r="BI1" s="1">
+        <v>269</v>
+      </c>
+      <c r="BJ1" s="1">
+        <v>270</v>
+      </c>
+      <c r="BK1" s="1">
+        <v>271</v>
+      </c>
+      <c r="BL1" s="1">
+        <v>272</v>
+      </c>
+      <c r="BM1" s="1">
+        <v>273</v>
+      </c>
+      <c r="BN1" s="1">
+        <v>274</v>
+      </c>
+      <c r="BO1" s="1">
+        <v>275</v>
+      </c>
+      <c r="BP1" s="1">
+        <v>276</v>
+      </c>
+      <c r="BQ1" s="1">
+        <v>277</v>
+      </c>
+      <c r="BR1" s="1">
+        <v>278</v>
+      </c>
+      <c r="BS1" s="1">
+        <v>279</v>
+      </c>
+      <c r="BT1" s="1">
+        <v>280</v>
+      </c>
+      <c r="BU1" s="1">
+        <v>281</v>
+      </c>
+      <c r="BV1" s="1">
+        <v>282</v>
+      </c>
+      <c r="BW1" s="1">
+        <v>283</v>
+      </c>
+      <c r="BX1" s="1">
+        <v>284</v>
+      </c>
+      <c r="BY1" s="1">
+        <v>285</v>
+      </c>
+      <c r="BZ1" s="1">
+        <v>286</v>
+      </c>
+      <c r="CA1" s="1">
+        <v>287</v>
+      </c>
+      <c r="CB1" s="1">
+        <v>288</v>
+      </c>
+      <c r="CC1" s="1">
+        <v>289</v>
+      </c>
+      <c r="CD1" s="1">
+        <v>290</v>
+      </c>
+      <c r="CE1" s="1">
+        <v>291</v>
+      </c>
+      <c r="CF1" s="1">
+        <v>292</v>
+      </c>
+      <c r="CG1" s="1">
+        <v>293</v>
+      </c>
+      <c r="CH1" s="1">
+        <v>294</v>
+      </c>
+      <c r="CI1" s="1">
+        <v>295</v>
+      </c>
+      <c r="CJ1" s="1">
+        <v>296</v>
+      </c>
+      <c r="CK1" s="1">
+        <v>297</v>
+      </c>
+      <c r="CL1" s="1">
+        <v>298</v>
+      </c>
+      <c r="CM1" s="1">
+        <v>299</v>
+      </c>
+      <c r="CN1" s="1">
+        <v>300</v>
+      </c>
+      <c r="CO1" s="1">
+        <v>301</v>
+      </c>
+      <c r="CP1" s="1">
+        <v>302</v>
+      </c>
+      <c r="CQ1" s="1">
+        <v>303</v>
+      </c>
+      <c r="CR1" s="1">
+        <v>304</v>
+      </c>
+      <c r="CS1" s="1">
+        <v>305</v>
+      </c>
+      <c r="CT1" s="1">
+        <v>306</v>
+      </c>
+      <c r="CU1" s="1">
+        <v>307</v>
+      </c>
+      <c r="CV1" s="1">
+        <v>308</v>
+      </c>
+      <c r="CW1" s="1">
+        <v>309</v>
+      </c>
+      <c r="CX1" s="1">
+        <v>310</v>
+      </c>
+      <c r="CY1" s="1">
+        <v>311</v>
+      </c>
+      <c r="CZ1" s="1">
+        <v>312</v>
+      </c>
+      <c r="DA1" s="1">
+        <v>313</v>
+      </c>
+      <c r="DB1" s="1">
+        <v>314</v>
+      </c>
+      <c r="DC1" s="1">
+        <v>315</v>
+      </c>
+      <c r="DD1" s="1">
+        <v>316</v>
+      </c>
+      <c r="DE1" s="1">
+        <v>317</v>
+      </c>
+      <c r="DF1" s="1">
+        <v>318</v>
+      </c>
+      <c r="DG1" s="1">
+        <v>319</v>
+      </c>
+      <c r="DH1" s="1">
+        <v>320</v>
+      </c>
+      <c r="DI1" s="1">
+        <v>321</v>
+      </c>
+      <c r="DJ1" s="1">
+        <v>322</v>
+      </c>
+      <c r="DK1" s="1">
+        <v>323</v>
+      </c>
+      <c r="DL1" s="1">
+        <v>324</v>
+      </c>
+      <c r="DM1" s="1">
+        <v>325</v>
+      </c>
+      <c r="DN1" s="1">
+        <v>326</v>
+      </c>
+      <c r="DO1" s="1">
+        <v>327</v>
+      </c>
+      <c r="DP1" s="1">
+        <v>328</v>
+      </c>
+      <c r="DQ1" s="1">
+        <v>329</v>
+      </c>
+      <c r="DR1" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:122" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>38.800000000000004</v>
+      </c>
+      <c r="C2">
+        <v>36.51</v>
+      </c>
+      <c r="D2">
+        <v>34.22</v>
+      </c>
+      <c r="E2">
+        <v>32.03</v>
+      </c>
+      <c r="F2">
+        <v>30.04</v>
+      </c>
+      <c r="G2">
+        <v>28.15</v>
+      </c>
+      <c r="H2">
+        <v>26.36</v>
+      </c>
+      <c r="I2">
+        <v>24.770000000000003</v>
+      </c>
+      <c r="J2">
+        <v>23.28</v>
+      </c>
+      <c r="K2">
+        <v>21.990000000000002</v>
+      </c>
+      <c r="L2">
+        <v>20.7</v>
+      </c>
+      <c r="M2">
+        <v>19.510000000000002</v>
+      </c>
+      <c r="N2">
+        <v>18.52</v>
+      </c>
+      <c r="O2">
+        <v>17.53</v>
+      </c>
+      <c r="P2">
+        <v>16.54</v>
+      </c>
+      <c r="Q2">
+        <v>15.75</v>
+      </c>
+      <c r="R2">
+        <v>14.959999999999999</v>
+      </c>
+      <c r="S2">
+        <v>14.17</v>
+      </c>
+      <c r="T2">
+        <v>13.479999999999999</v>
+      </c>
+      <c r="U2">
+        <v>12.889999999999999</v>
+      </c>
+      <c r="V2">
+        <v>12.200000000000001</v>
+      </c>
+      <c r="W2">
+        <v>11.71</v>
+      </c>
+      <c r="X2">
+        <v>11.120000000000001</v>
+      </c>
+      <c r="Y2">
+        <v>10.63</v>
+      </c>
+      <c r="Z2">
+        <v>10.14</v>
+      </c>
+      <c r="AA2">
+        <v>9.75</v>
+      </c>
+      <c r="AB2">
+        <v>9.26</v>
+      </c>
+      <c r="AC2">
+        <v>8.9699999999999989</v>
+      </c>
+      <c r="AD2">
+        <v>8.6800000000000015</v>
+      </c>
+      <c r="AE2">
+        <v>8.39</v>
+      </c>
+      <c r="AF2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="AG2">
+        <v>8.11</v>
+      </c>
+      <c r="AH2">
+        <v>8.120000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="AJ2">
+        <v>8.14</v>
+      </c>
+      <c r="AK2">
+        <v>8.35</v>
+      </c>
+      <c r="AL2">
+        <v>8.4600000000000009</v>
+      </c>
+      <c r="AM2">
+        <v>8.67</v>
+      </c>
+      <c r="AN2">
+        <v>8.98</v>
+      </c>
+      <c r="AO2">
+        <v>9.2900000000000009</v>
+      </c>
+      <c r="AP2">
+        <v>9.6</v>
+      </c>
+      <c r="AQ2">
+        <v>9.91</v>
+      </c>
+      <c r="AR2">
+        <v>10.219999999999999</v>
+      </c>
+      <c r="AS2">
+        <v>10.53</v>
+      </c>
+      <c r="AT2">
+        <v>10.940000000000001</v>
+      </c>
+      <c r="AU2">
+        <v>11.25</v>
+      </c>
+      <c r="AV2">
+        <v>11.66</v>
+      </c>
+      <c r="AW2">
+        <v>11.97</v>
+      </c>
+      <c r="AX2">
+        <v>12.28</v>
+      </c>
+      <c r="AY2">
+        <v>12.59</v>
+      </c>
+      <c r="AZ2">
+        <v>12.9</v>
+      </c>
+      <c r="BA2">
+        <v>13.209999999999999</v>
+      </c>
+      <c r="BB2">
+        <v>13.42</v>
+      </c>
+      <c r="BC2">
+        <v>13.63</v>
+      </c>
+      <c r="BD2">
+        <v>13.84</v>
+      </c>
+      <c r="BE2">
+        <v>13.950000000000001</v>
+      </c>
+      <c r="BF2">
+        <v>14.06</v>
+      </c>
+      <c r="BG2">
+        <v>14.17</v>
+      </c>
+      <c r="BH2">
+        <v>14.18</v>
+      </c>
+      <c r="BI2">
+        <v>14.29</v>
+      </c>
+      <c r="BJ2">
+        <v>14.399999999999999</v>
+      </c>
+      <c r="BK2">
+        <v>14.510000000000002</v>
+      </c>
+      <c r="BL2">
+        <v>14.42</v>
+      </c>
+      <c r="BM2">
+        <v>14.23</v>
+      </c>
+      <c r="BN2">
+        <v>13.94</v>
+      </c>
+      <c r="BO2">
+        <v>13.55</v>
+      </c>
+      <c r="BP2">
+        <v>13.26</v>
+      </c>
+      <c r="BQ2">
+        <v>12.969999999999999</v>
+      </c>
+      <c r="BR2">
+        <v>12.78</v>
+      </c>
+      <c r="BS2">
+        <v>12.59</v>
+      </c>
+      <c r="BT2">
+        <v>12.4</v>
+      </c>
+      <c r="BU2">
+        <v>12.110000000000001</v>
+      </c>
+      <c r="BV2">
+        <v>11.52</v>
+      </c>
+      <c r="BW2">
+        <v>10.83</v>
+      </c>
+      <c r="BX2">
+        <v>10.14</v>
+      </c>
+      <c r="BY2">
+        <v>9.35</v>
+      </c>
+      <c r="BZ2">
+        <v>8.76</v>
+      </c>
+      <c r="CA2">
+        <v>8.17</v>
+      </c>
+      <c r="CB2">
+        <v>7.68</v>
+      </c>
+      <c r="CC2">
+        <v>7.29</v>
+      </c>
+      <c r="CD2">
+        <v>6.9</v>
+      </c>
+      <c r="CE2">
+        <v>6.51</v>
+      </c>
+      <c r="CF2">
+        <v>6.22</v>
+      </c>
+      <c r="CG2">
+        <v>5.93</v>
+      </c>
+      <c r="CH2">
+        <v>5.54</v>
+      </c>
+      <c r="CI2">
+        <v>5.3500000000000005</v>
+      </c>
+      <c r="CJ2">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="CK2">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="CL2">
+        <v>4.58</v>
+      </c>
+      <c r="CM2">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="CN2">
+        <v>4.2</v>
+      </c>
+      <c r="CO2">
+        <v>4.01</v>
+      </c>
+      <c r="CP2">
+        <v>3.82</v>
+      </c>
+      <c r="CQ2">
+        <v>3.7300000000000004</v>
+      </c>
+      <c r="CR2">
+        <v>3.54</v>
+      </c>
+      <c r="CS2">
+        <v>3.3499999999999996</v>
+      </c>
+      <c r="CT2">
+        <v>3.2600000000000002</v>
+      </c>
+      <c r="CU2">
+        <v>3.17</v>
+      </c>
+      <c r="CV2">
+        <v>3.08</v>
+      </c>
+      <c r="CW2">
+        <v>2.99</v>
+      </c>
+      <c r="CX2">
+        <v>2.9000000000000004</v>
+      </c>
+      <c r="CY2">
+        <v>2.81</v>
+      </c>
+      <c r="CZ2">
+        <v>2.72</v>
+      </c>
+      <c r="DA2">
+        <v>2.63</v>
+      </c>
+      <c r="DB2">
+        <v>2.64</v>
+      </c>
+      <c r="DC2">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="DD2">
+        <v>2.46</v>
+      </c>
+      <c r="DE2">
+        <v>2.4699999999999998</v>
+      </c>
+      <c r="DF2">
+        <v>2.38</v>
+      </c>
+      <c r="DG2">
+        <v>2.3899999999999997</v>
+      </c>
+      <c r="DH2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="DI2">
+        <v>2.31</v>
+      </c>
+      <c r="DJ2">
+        <v>2.2199999999999998</v>
+      </c>
+      <c r="DK2">
+        <v>2.23</v>
+      </c>
+      <c r="DL2">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="DM2">
+        <v>2.15</v>
+      </c>
+      <c r="DN2">
+        <v>2.16</v>
+      </c>
+      <c r="DO2">
+        <v>2.17</v>
+      </c>
+      <c r="DP2">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="DQ2">
+        <v>2.09</v>
+      </c>
+      <c r="DR2">
+        <v>2.1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
